--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_伸びが未設定に戻る件_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_伸びが未設定に戻る件_20260928.xlsx
@@ -1046,7 +1046,7 @@
         <v>2889</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6095</v>
+        <v>6048</v>
       </c>
     </row>
   </sheetData>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>月額6,000円台（当方の算定は6,095円）</t>
+          <t>月額6,000円台（当方の算定は6,048円）</t>
         </is>
       </c>
     </row>
